--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486476_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486476_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2072</v>
+        <v>6.8287</v>
       </c>
       <c r="E2" t="n">
-        <v>4.03</v>
+        <v>3.6515</v>
       </c>
       <c r="F2" t="n">
         <v>3.1772</v>
@@ -610,10 +610,10 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9816</v>
+        <v>1.6031</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3772</v>
+        <v>0.9986</v>
       </c>
       <c r="U2" t="n">
         <v>0.6044</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4606</v>
+        <v>3.952</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3271</v>
+        <v>2.88</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1336</v>
+        <v>1.0719</v>
       </c>
       <c r="G3" t="n">
         <v>2.2081</v>
@@ -688,13 +688,13 @@
         <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6425</v>
+        <v>1.1338</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4456</v>
+        <v>0.9986</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1968</v>
+        <v>0.1352</v>
       </c>
       <c r="V3" t="n">
         <v>-1.13</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0566</v>
+        <v>3.6191</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1893</v>
+        <v>0.4128</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8673</v>
+        <v>3.2063</v>
       </c>
       <c r="G4" t="n">
         <v>1.926</v>
@@ -766,13 +766,13 @@
         <v>2.3926</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1131</v>
+        <v>0.6757</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5636</v>
+        <v>0.7871</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4505</v>
+        <v>-0.1115</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2875</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8061</v>
+        <v>2.84</v>
       </c>
       <c r="E5" t="n">
-        <v>0.913</v>
+        <v>1.3168</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8931</v>
+        <v>1.5233</v>
       </c>
       <c r="G5" t="n">
         <v>1.9296</v>
@@ -844,13 +844,13 @@
         <v>2.6101</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7688</v>
+        <v>0.8027</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4951</v>
+        <v>0.8989</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2737</v>
+        <v>-0.0961</v>
       </c>
       <c r="V5" t="n">
         <v>0.7602</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. BARTON</t>
+          <t>J. GRANGER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4552</v>
+        <v>2.7033</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6605</v>
+        <v>0.9417</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2054</v>
+        <v>1.7616</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0969</v>
+        <v>0.8695000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3662</v>
+        <v>3.7167</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7307</v>
+        <v>-2.8472</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9823</v>
+        <v>0.1182</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3177</v>
+        <v>3.288</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6647</v>
+        <v>-3.1698</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8854</v>
+        <v>0.7513</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0486</v>
+        <v>0.4286</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9339</v>
+        <v>0.3227</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0102</v>
+        <v>-0.4882</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3425</v>
+        <v>-0.3064</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3527</v>
+        <v>-0.1818</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3045</v>
+        <v>1.017</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0207</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3252</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. MC GREW</t>
+          <t>C. BARTON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2929</v>
+        <v>2.5246</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1597</v>
+        <v>3.884</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1332</v>
+        <v>-1.3595</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5697</v>
+        <v>3.0969</v>
       </c>
       <c r="H7" t="n">
-        <v>1.314</v>
+        <v>2.3662</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2558</v>
+        <v>0.7307</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7451</v>
+        <v>3.9823</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2989</v>
+        <v>2.3177</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5538</v>
+        <v>1.6647</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8247</v>
+        <v>-0.8854</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0151</v>
+        <v>0.0486</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8096</v>
+        <v>-0.9339</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>0.721</v>
+        <v>0.0796</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4146</v>
+        <v>-0.119</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3064</v>
+        <v>0.1986</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5204</v>
+        <v>-1.3045</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.0207</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5204</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GRANGER</t>
+          <t>T. MC GREW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9104</v>
+        <v>2.2929</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4262</v>
+        <v>1.1597</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4842</v>
+        <v>1.1332</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8695000000000001</v>
+        <v>1.5697</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7167</v>
+        <v>1.314</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.8472</v>
+        <v>0.2558</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1182</v>
+        <v>0.7451</v>
       </c>
       <c r="K8" t="n">
-        <v>3.288</v>
+        <v>1.2989</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.1698</v>
+        <v>-0.5538</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7513</v>
+        <v>0.8247</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4286</v>
+        <v>0.0151</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3227</v>
+        <v>0.8096</v>
       </c>
       <c r="P8" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2811</v>
+        <v>0.721</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.822</v>
+        <v>0.4146</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4592</v>
+        <v>0.3064</v>
       </c>
       <c r="V8" t="n">
-        <v>1.017</v>
+        <v>-1.5204</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.113</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>R. STUMBRIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2406</v>
+        <v>1.3882</v>
       </c>
       <c r="E9" t="n">
-        <v>0.334</v>
+        <v>2.4596</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9066</v>
+        <v>-1.0713</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3382</v>
+        <v>0.8938</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0029</v>
+        <v>1.3289</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3411</v>
+        <v>-0.4351</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0451</v>
+        <v>0.921</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2801</v>
+        <v>0.7847</v>
       </c>
       <c r="L9" t="n">
-        <v>0.765</v>
+        <v>0.1363</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2932</v>
+        <v>-0.0272</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2829</v>
+        <v>0.5442</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5760999999999999</v>
+        <v>-0.5714</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6525</v>
+        <v>1.7401</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6679</v>
+        <v>-0.1157</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3341</v>
+        <v>0.4086</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3338</v>
+        <v>-0.5242</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.113</v>
+        <v>-1.13</v>
       </c>
       <c r="W9" t="n">
         <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.243</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6686</v>
+        <v>0.9122</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2255</v>
+        <v>0.0673</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4431</v>
+        <v>0.8449</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0729</v>
+        <v>1.3382</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1008</v>
+        <v>-0.0029</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0279</v>
+        <v>1.3411</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7151999999999999</v>
+        <v>1.0451</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6387</v>
+        <v>0.2801</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0765</v>
+        <v>0.765</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3577</v>
+        <v>0.2932</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4621</v>
+        <v>-0.2829</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1044</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.87</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2705</v>
+        <v>0.3395</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4026</v>
+        <v>0.0673</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1321</v>
+        <v>0.2722</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1952</v>
+        <v>-0.113</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. STUMBRIS</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4951</v>
+        <v>0.1677</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7205</v>
+        <v>0.002</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2255</v>
+        <v>0.1657</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8938</v>
+        <v>1.0729</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3289</v>
+        <v>1.1008</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4351</v>
+        <v>-0.0279</v>
       </c>
       <c r="J11" t="n">
-        <v>0.921</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7847</v>
+        <v>0.6387</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1363</v>
+        <v>0.0765</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0272</v>
+        <v>0.3577</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5442</v>
+        <v>0.4621</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5714</v>
+        <v>-0.1044</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7401</v>
+        <v>-0.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7401</v>
+        <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0088</v>
+        <v>-0.2304</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3305</v>
+        <v>0.1791</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6784</v>
+        <v>-0.4095</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0207</v>
+        <v>-0.487</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4658</v>
+        <v>0.907</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4865</v>
+        <v>-1.3941</v>
       </c>
       <c r="G12" t="n">
         <v>2.0389</v>
@@ -1390,13 +1390,13 @@
         <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0994</v>
+        <v>-0.5657</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7367</v>
+        <v>0.1779</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.836</v>
+        <v>-0.7436</v>
       </c>
       <c r="V12" t="n">
         <v>-2.1777</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.9414</v>
+        <v>-0.768</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0995</v>
+        <v>-0.9878</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1582</v>
+        <v>0.2198</v>
       </c>
       <c r="G13" t="n">
         <v>0.8501</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.704</v>
+        <v>-0.5306</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6355</v>
+        <v>-0.5738</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>25.6312</v>
+        <v>25.9737</v>
       </c>
       <c r="E14" t="n">
-        <v>16.3521</v>
+        <v>16.6946</v>
       </c>
       <c r="F14" t="n">
-        <v>9.279100000000001</v>
+        <v>9.279</v>
       </c>
       <c r="G14" t="n">
         <v>19.5674</v>
@@ -1525,7 +1525,7 @@
         <v>15.7714</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.0914</v>
+        <v>-1.091399999999999</v>
       </c>
       <c r="M14" t="n">
         <v>4.8877</v>
@@ -1546,13 +1546,13 @@
         <v>17.4005</v>
       </c>
       <c r="S14" t="n">
-        <v>3.082300000000001</v>
+        <v>3.424799999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>4.206</v>
+        <v>4.548600000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1239</v>
+        <v>-1.1237</v>
       </c>
       <c r="V14" t="n">
         <v>-3.5438</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8007</v>
+        <v>1.8237</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0462</v>
+        <v>2.8227</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2456</v>
+        <v>-0.999</v>
       </c>
       <c r="G15" t="n">
         <v>0.5501</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.291</v>
+        <v>-0.268</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0721</v>
+        <v>-0.1514</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3632</v>
+        <v>-0.1166</v>
       </c>
       <c r="V15" t="n">
         <v>3.9342</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4288</v>
+        <v>0.4172</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3689</v>
+        <v>-0.2572</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7977</v>
+        <v>0.6744</v>
       </c>
       <c r="G16" t="n">
         <v>0.8471</v>
@@ -1702,13 +1702,13 @@
         <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6268</v>
+        <v>0.6153</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7006</v>
+        <v>0.8124</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0738</v>
+        <v>-0.1971</v>
       </c>
       <c r="V16" t="n">
         <v>1.13</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.37</v>
+        <v>0.3199</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5051</v>
+        <v>0.3934</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1351</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6679</v>
@@ -1780,13 +1780,13 @@
         <v>0.435</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7982</v>
+        <v>0.7481</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9061</v>
+        <v>0.7943</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1079</v>
+        <v>-0.0463</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1952</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1054</v>
+        <v>-0.8992</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6998</v>
+        <v>-1.3704</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5944</v>
+        <v>0.4712</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2083</v>
@@ -1858,13 +1858,13 @@
         <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9729</v>
+        <v>0.1791</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5997</v>
+        <v>-0.0709</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3732</v>
+        <v>0.2499</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1804</v>
+        <v>-0.9068000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7634</v>
+        <v>-0.4281</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.417</v>
+        <v>-0.4786</v>
       </c>
       <c r="G19" t="n">
         <v>-3.4063</v>
@@ -1936,13 +1936,13 @@
         <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1216</v>
+        <v>0.152</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4675</v>
+        <v>-0.1322</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3458</v>
+        <v>0.2842</v>
       </c>
       <c r="V19" t="n">
         <v>1.695</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. BRACEY</t>
+          <t>J. MARTINEZ CABEZUDO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5223</v>
+        <v>-1.03</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1041</v>
+        <v>-0.7581</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4182</v>
+        <v>-0.2719</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5790999999999999</v>
+        <v>-1.6573</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1405</v>
+        <v>0.2615</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7196</v>
+        <v>-1.9188</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4509</v>
+        <v>-1.1234</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1611</v>
+        <v>0.3285</v>
       </c>
       <c r="L20" t="n">
-        <v>0.612</v>
+        <v>-1.4519</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1282</v>
+        <v>-0.5339</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9794</v>
+        <v>-0.067</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1076</v>
+        <v>-0.467</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3613</v>
+        <v>0.17</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6201</v>
+        <v>0.3653</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9814000000000001</v>
+        <v>-0.1953</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MARTINEZ CABEZUDO</t>
+          <t>L. BRACEY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6504</v>
+        <v>-1.4671</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3168</v>
+        <v>-1.4393</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3336</v>
+        <v>-0.0277</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6573</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2615</v>
+        <v>-1.1405</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9188</v>
+        <v>1.7196</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1234</v>
+        <v>0.4509</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3285</v>
+        <v>-0.1611</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4519</v>
+        <v>0.612</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5339</v>
+        <v>0.1282</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.067</v>
+        <v>-0.9794</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.467</v>
+        <v>1.1076</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6525</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4504</v>
+        <v>-0.3061</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1935</v>
+        <v>0.2848</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2569</v>
+        <v>-0.5909</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0412</v>
+        <v>-1.7754</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5665</v>
+        <v>-1.4547</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4747</v>
+        <v>-0.3206</v>
       </c>
       <c r="G22" t="n">
         <v>-3.6918</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9367</v>
+        <v>-0.6708</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4074</v>
+        <v>-0.2956</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5294</v>
+        <v>-0.3752</v>
       </c>
       <c r="V22" t="n">
         <v>1.4997</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3175</v>
+        <v>-2.6014</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0469</v>
+        <v>-1.3822</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2706</v>
+        <v>-1.2192</v>
       </c>
       <c r="G23" t="n">
         <v>-3.1379</v>
@@ -2248,13 +2248,13 @@
         <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1901</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.5624</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7076</v>
+        <v>-0.6561</v>
       </c>
       <c r="V23" t="n">
         <v>0.1952</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4321</v>
+        <v>-4.5002</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9151</v>
+        <v>-1.2504</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.517</v>
+        <v>-3.2498</v>
       </c>
       <c r="G24" t="n">
         <v>-1.1288</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4556</v>
+        <v>-0.5236</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2211</v>
+        <v>-0.1142</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6767</v>
+        <v>-0.4095</v>
       </c>
       <c r="V24" t="n">
         <v>-1.3252</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.4298</v>
+        <v>-5.8697</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.1843</v>
+        <v>-2.7373</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.2455</v>
+        <v>-3.1324</v>
       </c>
       <c r="G25" t="n">
         <v>-4.0287</v>
@@ -2404,13 +2404,13 @@
         <v>1.0875</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5088</v>
+        <v>-0.9487</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2209</v>
+        <v>-0.7739</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2879</v>
+        <v>-0.1749</v>
       </c>
       <c r="V25" t="n">
         <v>0.1952</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.551600000000001</v>
+        <v>-7.6524</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.8646</v>
+        <v>-1.4176</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.6869</v>
+        <v>-6.2348</v>
       </c>
       <c r="G26" t="n">
         <v>-3.6169</v>
@@ -2482,13 +2482,13 @@
         <v>1.0875</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.5448</v>
+        <v>-0.6456</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6044</v>
+        <v>-0.1574</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9403</v>
+        <v>-0.4882</v>
       </c>
       <c r="V26" t="n">
         <v>-3.3899</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-25.6312</v>
+        <v>-24.1414</v>
       </c>
       <c r="E27" t="n">
-        <v>-9.2791</v>
+        <v>-9.279199999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-16.3521</v>
+        <v>-14.8618</v>
       </c>
       <c r="G27" t="n">
         <v>-19.5676</v>
@@ -2551,7 +2551,7 @@
         <v>1.091399999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>-6.525300000000001</v>
+        <v>-6.5253</v>
       </c>
       <c r="Q27" t="n">
         <v>-17.4006</v>
@@ -2560,13 +2560,13 @@
         <v>10.875</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.0822</v>
+        <v>-1.592</v>
       </c>
       <c r="T27" t="n">
-        <v>1.1237</v>
+        <v>1.1236</v>
       </c>
       <c r="U27" t="n">
-        <v>-4.206099999999999</v>
+        <v>-2.716</v>
       </c>
       <c r="V27" t="n">
         <v>3.543800000000001</v>
